--- a/data/metas.xlsx
+++ b/data/metas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvsjulio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1001" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C0C34E5-BC15-4067-868D-6877392D6780}"/>
+  <xr:revisionPtr revIDLastSave="1008" documentId="8_{787D9E49-702D-43BD-B99B-4B64F775E77B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5791BF8-420D-4072-89E6-3A83F64CD4D4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D1391136-BBFC-43C7-B899-B77B0ECC5956}"/>
   </bookViews>
@@ -2610,7 +2610,7 @@
         <v>22</v>
       </c>
       <c r="D122" s="2">
-        <v>27700</v>
+        <v>600</v>
       </c>
       <c r="E122" s="2">
         <v>55350</v>
@@ -2627,7 +2627,7 @@
         <v>27</v>
       </c>
       <c r="D123" s="2">
-        <v>930</v>
+        <v>10</v>
       </c>
       <c r="E123" s="2">
         <v>55350</v>
@@ -2644,7 +2644,7 @@
         <v>28</v>
       </c>
       <c r="D124" s="2">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="E124" s="2">
         <v>55350</v>
@@ -2661,7 +2661,7 @@
         <v>29</v>
       </c>
       <c r="D125" s="2">
-        <v>1712</v>
+        <v>10</v>
       </c>
       <c r="E125" s="2">
         <v>55350</v>
@@ -2678,7 +2678,7 @@
         <v>30</v>
       </c>
       <c r="D126" s="2">
-        <v>3255</v>
+        <v>20</v>
       </c>
       <c r="E126" s="2">
         <v>55350</v>
